--- a/appointment_forms/029_gravesite_maintenance_scheduling_request--appointment_forms.xlsx
+++ b/appointment_forms/029_gravesite_maintenance_scheduling_request--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'maintenance',_'value':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Maintenance', 'value': 'maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'decoration',_'value':_'decoration'}</t>
+          <t>decoration</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Decoration', 'value': 'decoration'}</t>
+          <t>Decoration</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'data_collection',_'value':_'data_collection'}</t>
+          <t>data_collection</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Data Collection', 'value': 'data_collection'}</t>
+          <t>Data Collection</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'grave_maintenance',_'value':_'grave_maintenance'}</t>
+          <t>grave_maintenance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Grave Maintenance', 'value': 'grave_maintenance'}</t>
+          <t>Grave Maintenance</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'headstone_repair',_'value':_'headstone_repair'}</t>
+          <t>headstone_repair</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Headstone Repair', 'value': 'headstone_repair'}</t>
+          <t>Headstone Repair</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'memorial_stone_replacement',_'value':_'memorial_stone_replacement'}</t>
+          <t>memorial_stone_replacement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Memorial Stone Replacement', 'value': 'memorial_stone_replacement'}</t>
+          <t>Memorial Stone Replacement</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'adult',_'value':_'adult'}</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Adult', 'value': 'adult'}</t>
+          <t>Adult</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'child',_'value':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Child', 'value': 'child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'infant',_'value':_'infant'}</t>
+          <t>infant</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Infant', 'value': 'infant'}</t>
+          <t>Infant</t>
         </is>
       </c>
     </row>
